--- a/Distribucion/Excels/EREDES.xlsx
+++ b/Distribucion/Excels/EREDES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,16 @@
           <t>Subestacion_EREDES</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Longitud</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Latitud</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -477,6 +487,12 @@
           <t>SE/CR ZORRINA</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>-6.243722329211872</v>
+      </c>
+      <c r="G2" t="n">
+        <v>43.40423007016015</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -500,6 +516,12 @@
           <t>SE/CR VILLAMAYOR</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>-5.30956268896188</v>
+      </c>
+      <c r="G3" t="n">
+        <v>43.36166549797462</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +545,12 @@
           <t>SE/CR VENTA LAS RANAS</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>-5.507364971779426</v>
+      </c>
+      <c r="G4" t="n">
+        <v>43.51382652357489</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,6 +574,12 @@
           <t>SE/CR VEGUIN 2</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>-5.777244700704862</v>
+      </c>
+      <c r="G5" t="n">
+        <v>43.32965206422116</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,6 +603,12 @@
           <t>SE/CR URB LA VALLINA 1</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>-5.797536084144692</v>
+      </c>
+      <c r="G6" t="n">
+        <v>43.61139725656262</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -592,6 +632,12 @@
           <t>SE/CR TANES</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>-5.446109301722255</v>
+      </c>
+      <c r="G7" t="n">
+        <v>43.22241801284392</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,6 +661,12 @@
           <t>SE/CR SECTOR 4</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>-3.726057346225845</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40.25074248606446</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -638,6 +690,12 @@
           <t>SE/CR SECTOR 13</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>-0.5513364495928941</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.47656310040726</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +719,12 @@
           <t>SE/CR SANTA EULALIA</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>-5.878996523890197</v>
+      </c>
+      <c r="G10" t="n">
+        <v>43.28389619268847</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,6 +748,12 @@
           <t>SE/CR SANDIN</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>-5.695588776424853</v>
+      </c>
+      <c r="G11" t="n">
+        <v>43.31515269439987</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,6 +777,12 @@
           <t>SE/CR SAN PEDRO</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>-6.113516719114049</v>
+      </c>
+      <c r="G12" t="n">
+        <v>43.33664010341921</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -730,6 +806,12 @@
           <t>SE/CR SAN MIGUEL</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>-5.743468716439236</v>
+      </c>
+      <c r="G13" t="n">
+        <v>43.38749649272513</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -754,6 +836,12 @@
 PRAVIA</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>-6.087345073465281</v>
+      </c>
+      <c r="G14" t="n">
+        <v>43.55154199568497</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -777,6 +865,12 @@
           <t>SE/CR SAMA</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>-5.675850624157039</v>
+      </c>
+      <c r="G15" t="n">
+        <v>43.29292772470937</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -801,6 +895,12 @@
 RESIDENCIAL</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>-5.66362682306143</v>
+      </c>
+      <c r="G16" t="n">
+        <v>43.51335593219567</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -824,6 +924,12 @@
           <t>SE/CR RIOSECO</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>-5.457733286947625</v>
+      </c>
+      <c r="G17" t="n">
+        <v>43.221842778572</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -847,6 +953,12 @@
           <t>SE/CR RIAÑO</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>-5.717536777636216</v>
+      </c>
+      <c r="G18" t="n">
+        <v>43.32329127758536</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -870,6 +982,12 @@
           <t>SE/CR QUINTES</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>-5.549606423768729</v>
+      </c>
+      <c r="G19" t="n">
+        <v>43.52569826350171</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -893,6 +1011,12 @@
           <t>SE/CR PROAZA</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>-6.018561244200434</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43.24923204463798</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -916,6 +1040,12 @@
           <t>SE/CR POSTIGO</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>-5.840151785703897</v>
+      </c>
+      <c r="G21" t="n">
+        <v>43.36199230624374</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -939,6 +1069,12 @@
           <t>SE/CR PIEDELORO</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>-5.79984497782556</v>
+      </c>
+      <c r="G22" t="n">
+        <v>43.5714077688927</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -962,6 +1098,12 @@
           <t>SE/CR PGNO LOS AZARBES</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>-0.7382844001532174</v>
+      </c>
+      <c r="G23" t="n">
+        <v>38.14265999935877</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -985,6 +1127,12 @@
           <t>SE/CR PEON</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>-5.544304521190026</v>
+      </c>
+      <c r="G24" t="n">
+        <v>43.48795432270181</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1009,6 +1157,12 @@
 CONGRESOS</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>-5.859705599579583</v>
+      </c>
+      <c r="G25" t="n">
+        <v>43.35910332658035</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1032,6 +1186,12 @@
           <t>SE/CR OXIGENO</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>-5.693808312745514</v>
+      </c>
+      <c r="G26" t="n">
+        <v>43.54123537069653</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1055,6 +1215,12 @@
           <t>SE/CR NUEVA</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>-4.942400910804978</v>
+      </c>
+      <c r="G27" t="n">
+        <v>43.43290995128635</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1078,6 +1244,12 @@
           <t>SE/CR NOCEDA</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>-5.183670336165914</v>
+      </c>
+      <c r="G28" t="n">
+        <v>43.3920805403917</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1101,6 +1273,12 @@
           <t>SE/CR NIEDA</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>-5.110049518328766</v>
+      </c>
+      <c r="G29" t="n">
+        <v>43.34917008708607</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1124,6 +1302,12 @@
           <t>SE/CR NARANCO</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>-5.855822635955099</v>
+      </c>
+      <c r="G30" t="n">
+        <v>43.36988666312457</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1147,6 +1331,12 @@
           <t>SE/CR MIRANDA</t>
         </is>
       </c>
+      <c r="F31" t="n">
+        <v>-5.947662935852986</v>
+      </c>
+      <c r="G31" t="n">
+        <v>43.5402103326235</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1170,6 +1360,12 @@
           <t>SE/CR MASIA BALO</t>
         </is>
       </c>
+      <c r="F32" t="n">
+        <v>-0.5784893017994105</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39.48060150903018</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1193,6 +1389,12 @@
           <t>SE/CR MALLADERA</t>
         </is>
       </c>
+      <c r="F33" t="n">
+        <v>-6.067309640219517</v>
+      </c>
+      <c r="G33" t="n">
+        <v>43.3885883037095</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1216,6 +1418,12 @@
           <t>SE/CR LUIÑA</t>
         </is>
       </c>
+      <c r="F34" t="n">
+        <v>-6.767696541846818</v>
+      </c>
+      <c r="G34" t="n">
+        <v>42.922850630306</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1240,6 +1448,12 @@
 CRUCERO</t>
         </is>
       </c>
+      <c r="F35" t="n">
+        <v>-6.380820728313885</v>
+      </c>
+      <c r="G35" t="n">
+        <v>43.35134996388585</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1263,6 +1477,12 @@
           <t>SE/CR LLEDIAS</t>
         </is>
       </c>
+      <c r="F36" t="n">
+        <v>-4.865858451323254</v>
+      </c>
+      <c r="G36" t="n">
+        <v>43.41491873745129</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1286,6 +1506,12 @@
           <t>SE/CR LIERES</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>-5.581942214853819</v>
+      </c>
+      <c r="G37" t="n">
+        <v>43.38170404107714</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1309,6 +1535,12 @@
           <t>SE/CR LAVIANA</t>
         </is>
       </c>
+      <c r="F38" t="n">
+        <v>-5.559243665699098</v>
+      </c>
+      <c r="G38" t="n">
+        <v>43.24250836440902</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1332,6 +1564,12 @@
           <t>SE/CR LAGUARRES</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>0.4486964669976489</v>
+      </c>
+      <c r="G39" t="n">
+        <v>42.20442107182719</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1355,6 +1593,12 @@
           <t>SE/CR LADA</t>
         </is>
       </c>
+      <c r="F40" t="n">
+        <v>-5.715414935443544</v>
+      </c>
+      <c r="G40" t="n">
+        <v>43.29924964357859</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1378,6 +1622,12 @@
           <t>SE/CR LA PINAETA</t>
         </is>
       </c>
+      <c r="F41" t="n">
+        <v>-0.2356679148714464</v>
+      </c>
+      <c r="G41" t="n">
+        <v>39.67165958209399</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1401,6 +1651,12 @@
           <t>SE/CR LA ESTRADA</t>
         </is>
       </c>
+      <c r="F42" t="n">
+        <v>-5.052242876160525</v>
+      </c>
+      <c r="G42" t="n">
+        <v>43.34400148565084</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1424,6 +1680,12 @@
           <t>SE/CR LA ESTACION</t>
         </is>
       </c>
+      <c r="F43" t="n">
+        <v>-6.110639260797432</v>
+      </c>
+      <c r="G43" t="n">
+        <v>43.49061795940048</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1447,6 +1709,12 @@
           <t>SE/CR LA CABAÑA</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>-5.649872980827768</v>
+      </c>
+      <c r="G44" t="n">
+        <v>43.40266501734791</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1470,6 +1738,12 @@
           <t>SE/CR LA BARRACA</t>
         </is>
       </c>
+      <c r="F45" t="n">
+        <v>-6.162732731488672</v>
+      </c>
+      <c r="G45" t="n">
+        <v>43.50306336406747</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1493,6 +1767,12 @@
           <t>SE/CR LA ARENA</t>
         </is>
       </c>
+      <c r="F46" t="n">
+        <v>-6.073811216786101</v>
+      </c>
+      <c r="G46" t="n">
+        <v>43.55721738456101</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1516,6 +1796,12 @@
           <t>SE/CR INSTITUTO</t>
         </is>
       </c>
+      <c r="F47" t="n">
+        <v>-6.553434439931141</v>
+      </c>
+      <c r="G47" t="n">
+        <v>43.17857177824941</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1539,6 +1825,12 @@
           <t>SE/CR IBIAS</t>
         </is>
       </c>
+      <c r="F48" t="n">
+        <v>-6.870204934689481</v>
+      </c>
+      <c r="G48" t="n">
+        <v>43.03173536874539</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1562,6 +1854,12 @@
           <t>SE/CR GRULLOS</t>
         </is>
       </c>
+      <c r="F49" t="n">
+        <v>-6.05379447227657</v>
+      </c>
+      <c r="G49" t="n">
+        <v>43.44253213868278</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1585,6 +1883,12 @@
           <t>SE/CR GETAFE SUR</t>
         </is>
       </c>
+      <c r="F50" t="n">
+        <v>-3.729689006608354</v>
+      </c>
+      <c r="G50" t="n">
+        <v>40.27402816098827</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1608,6 +1912,12 @@
           <t>SE/CR FERREROS</t>
         </is>
       </c>
+      <c r="F51" t="n">
+        <v>-5.372165959365053</v>
+      </c>
+      <c r="G51" t="n">
+        <v>43.34456438526159</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1631,6 +1941,12 @@
           <t>SE/CR EZCURDIA</t>
         </is>
       </c>
+      <c r="F52" t="n">
+        <v>-5.650400423887798</v>
+      </c>
+      <c r="G52" t="n">
+        <v>43.53930645642332</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1654,6 +1970,12 @@
           <t>SE/CR ENTRAGO</t>
         </is>
       </c>
+      <c r="F53" t="n">
+        <v>-6.098476906597787</v>
+      </c>
+      <c r="G53" t="n">
+        <v>43.17168445197187</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1677,6 +1999,12 @@
           <t>SE/CR EL RASO</t>
         </is>
       </c>
+      <c r="F54" t="n">
+        <v>-0.6866530276097721</v>
+      </c>
+      <c r="G54" t="n">
+        <v>38.05340377483826</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1700,6 +2028,12 @@
           <t>SE/CR EL PUELO</t>
         </is>
       </c>
+      <c r="F55" t="n">
+        <v>-6.529186773442041</v>
+      </c>
+      <c r="G55" t="n">
+        <v>43.22724877127121</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1723,6 +2057,12 @@
           <t>SE/CR EL LLANO</t>
         </is>
       </c>
+      <c r="F56" t="n">
+        <v>-5.664983981483027</v>
+      </c>
+      <c r="G56" t="n">
+        <v>43.53328253553471</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1746,6 +2086,12 @@
           <t>SE/CR EL FRESNO</t>
         </is>
       </c>
+      <c r="F57" t="n">
+        <v>-5.855257365022647</v>
+      </c>
+      <c r="G57" t="n">
+        <v>43.35656957720781</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1769,6 +2115,12 @@
           <t>SE/CR EL CRISTO</t>
         </is>
       </c>
+      <c r="F58" t="n">
+        <v>-5.86513597001837</v>
+      </c>
+      <c r="G58" t="n">
+        <v>43.35385355909192</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1792,6 +2144,12 @@
           <t>SE/CR EL COBAYO</t>
         </is>
       </c>
+      <c r="F59" t="n">
+        <v>-5.060546370354444</v>
+      </c>
+      <c r="G59" t="n">
+        <v>43.45635731330629</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1815,6 +2173,12 @@
           <t>SE/CR EL BERRON</t>
         </is>
       </c>
+      <c r="F60" t="n">
+        <v>-5.701385671812579</v>
+      </c>
+      <c r="G60" t="n">
+        <v>43.38644432631414</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1838,6 +2202,12 @@
           <t>SE/CR EDIFICIO SOCIAL</t>
         </is>
       </c>
+      <c r="F61" t="n">
+        <v>-5.851785611586386</v>
+      </c>
+      <c r="G61" t="n">
+        <v>43.35780813251858</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1861,6 +2231,12 @@
           <t>SE/CR DANONE (ALDAYA)</t>
         </is>
       </c>
+      <c r="F62" t="n">
+        <v>-0.4967596312964494</v>
+      </c>
+      <c r="G62" t="n">
+        <v>39.44724442938274</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1884,6 +2260,12 @@
           <t>SE/CR CTRA MADRID</t>
         </is>
       </c>
+      <c r="F63" t="n">
+        <v>-0.9475412066053361</v>
+      </c>
+      <c r="G63" t="n">
+        <v>41.64228551689076</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1907,6 +2289,12 @@
           <t>SE/CR COSTANILLA</t>
         </is>
       </c>
+      <c r="F64" t="n">
+        <v>-5.662756208068131</v>
+      </c>
+      <c r="G64" t="n">
+        <v>43.54031903261445</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1930,6 +2318,12 @@
           <t>SE/CR CORNELLANA</t>
         </is>
       </c>
+      <c r="F65" t="n">
+        <v>-6.15481517977792</v>
+      </c>
+      <c r="G65" t="n">
+        <v>43.41142164123818</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1953,6 +2347,12 @@
           <t>SE/CR COLINA DEL FAISAN</t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>-5.718471560529935</v>
+      </c>
+      <c r="G66" t="n">
+        <v>43.52550235091994</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1976,6 +2376,12 @@
           <t>SE/CR CLAS</t>
         </is>
       </c>
+      <c r="F67" t="n">
+        <v>-5.778210181400425</v>
+      </c>
+      <c r="G67" t="n">
+        <v>43.38704217495874</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1999,6 +2405,12 @@
           <t>SE/CR CASIELLES</t>
         </is>
       </c>
+      <c r="F68" t="n">
+        <v>-5.673505274722939</v>
+      </c>
+      <c r="G68" t="n">
+        <v>43.28628333345606</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2022,6 +2434,12 @@
           <t>SE/CR CARROCERA I</t>
         </is>
       </c>
+      <c r="F69" t="n">
+        <v>-5.623811946336648</v>
+      </c>
+      <c r="G69" t="n">
+        <v>43.28756734665058</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2045,6 +2463,12 @@
           <t>SE/CR CAÑO</t>
         </is>
       </c>
+      <c r="F70" t="n">
+        <v>-5.13947892331478</v>
+      </c>
+      <c r="G70" t="n">
+        <v>43.32369818153472</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2068,6 +2492,12 @@
           <t>SE/CR CABECERA</t>
         </is>
       </c>
+      <c r="F71" t="n">
+        <v>-0.2088864780382329</v>
+      </c>
+      <c r="G71" t="n">
+        <v>39.68134071396904</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2091,6 +2521,12 @@
           <t>SE/CR BONAIRE 3</t>
         </is>
       </c>
+      <c r="F72" t="n">
+        <v>-0.4871361629696649</v>
+      </c>
+      <c r="G72" t="n">
+        <v>39.47051918336894</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2114,6 +2550,12 @@
           <t>SE/CR BONAIRE 2</t>
         </is>
       </c>
+      <c r="F73" t="n">
+        <v>-0.4903417012723606</v>
+      </c>
+      <c r="G73" t="n">
+        <v>39.47240528459459</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2137,6 +2579,12 @@
           <t>SE/CR BONAIRE 1</t>
         </is>
       </c>
+      <c r="F74" t="n">
+        <v>-0.4903446438505746</v>
+      </c>
+      <c r="G74" t="n">
+        <v>39.47240426706473</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2160,6 +2608,12 @@
           <t>SE/CR BOCINES</t>
         </is>
       </c>
+      <c r="F75" t="n">
+        <v>-5.792220835236663</v>
+      </c>
+      <c r="G75" t="n">
+        <v>43.60872826659367</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2183,6 +2637,12 @@
           <t>SE/CR BLIMEA</t>
         </is>
       </c>
+      <c r="F76" t="n">
+        <v>-5.590492433216744</v>
+      </c>
+      <c r="G76" t="n">
+        <v>43.27007106759447</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2206,6 +2666,12 @@
           <t>SE/CR BIEDES</t>
         </is>
       </c>
+      <c r="F77" t="n">
+        <v>-5.937630552988924</v>
+      </c>
+      <c r="G77" t="n">
+        <v>43.4273505112372</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2229,6 +2695,12 @@
           <t>SE/CR BEETHOVEN 8</t>
         </is>
       </c>
+      <c r="F78" t="n">
+        <v>-0.9453099600688223</v>
+      </c>
+      <c r="G78" t="n">
+        <v>41.63369428097609</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2252,6 +2724,12 @@
           <t>SE/CR BEDRIÑANA</t>
         </is>
       </c>
+      <c r="F79" t="n">
+        <v>-5.437834131873944</v>
+      </c>
+      <c r="G79" t="n">
+        <v>43.49175589799071</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2275,6 +2753,12 @@
           <t>SE/CR BEBARES</t>
         </is>
       </c>
+      <c r="F80" t="n">
+        <v>-6.35555226874447</v>
+      </c>
+      <c r="G80" t="n">
+        <v>43.2903108329393</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2298,6 +2782,12 @@
           <t>SE/CR BARDAJI</t>
         </is>
       </c>
+      <c r="F81" t="n">
+        <v>0.3934148335718216</v>
+      </c>
+      <c r="G81" t="n">
+        <v>42.41897114122447</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2321,6 +2811,12 @@
           <t>SE/CR AVDA SANTANDER</t>
         </is>
       </c>
+      <c r="F82" t="n">
+        <v>-5.853284540826098</v>
+      </c>
+      <c r="G82" t="n">
+        <v>43.36768325268325</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2344,6 +2840,12 @@
           <t>SE/CR ASTURIAS</t>
         </is>
       </c>
+      <c r="F83" t="n">
+        <v>-0.442552613657628</v>
+      </c>
+      <c r="G83" t="n">
+        <v>39.53191787891437</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2367,6 +2869,12 @@
           <t>SE/CR AMBAS</t>
         </is>
       </c>
+      <c r="F84" t="n">
+        <v>-5.487131926209834</v>
+      </c>
+      <c r="G84" t="n">
+        <v>43.44755057328947</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2390,6 +2898,12 @@
           <t>SE/CR AEROPUERTO</t>
         </is>
       </c>
+      <c r="F85" t="n">
+        <v>-6.035229997722525</v>
+      </c>
+      <c r="G85" t="n">
+        <v>43.55833761510075</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2413,6 +2927,12 @@
           <t>SE/CR ABANTRO</t>
         </is>
       </c>
+      <c r="F86" t="n">
+        <v>-5.39099892981364</v>
+      </c>
+      <c r="G86" t="n">
+        <v>43.20278998614728</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2436,6 +2956,12 @@
           <t>SE VILLAVICIOSA</t>
         </is>
       </c>
+      <c r="F87" t="n">
+        <v>-5.433956479102171</v>
+      </c>
+      <c r="G87" t="n">
+        <v>43.47428259734419</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2459,6 +2985,12 @@
           <t>SE VILLALEGRE</t>
         </is>
       </c>
+      <c r="F88" t="n">
+        <v>-5.909443230693908</v>
+      </c>
+      <c r="G88" t="n">
+        <v>43.54634210382199</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2482,6 +3014,12 @@
           <t>SE VIDANOVA</t>
         </is>
       </c>
+      <c r="F89" t="n">
+        <v>-0.2662840774692838</v>
+      </c>
+      <c r="G89" t="n">
+        <v>39.67404886438688</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2505,6 +3043,12 @@
           <t>SE VEGUIN 1</t>
         </is>
       </c>
+      <c r="F90" t="n">
+        <v>-5.772721580124391</v>
+      </c>
+      <c r="G90" t="n">
+        <v>43.33003659789201</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2528,6 +3072,12 @@
           <t>SE VEGA RENGOS</t>
         </is>
       </c>
+      <c r="F91" t="n">
+        <v>-6.61427128025639</v>
+      </c>
+      <c r="G91" t="n">
+        <v>43.04980597251483</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2551,6 +3101,12 @@
           <t>SE TRASONA</t>
         </is>
       </c>
+      <c r="F92" t="n">
+        <v>-5.867856059647798</v>
+      </c>
+      <c r="G92" t="n">
+        <v>43.55182645805944</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2574,6 +3130,12 @@
           <t>SE TABIELLA</t>
         </is>
       </c>
+      <c r="F93" t="n">
+        <v>-5.898706713601531</v>
+      </c>
+      <c r="G93" t="n">
+        <v>43.57446717789744</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2597,6 +3159,12 @@
           <t>SE SOTO</t>
         </is>
       </c>
+      <c r="F94" t="n">
+        <v>-5.873531965123016</v>
+      </c>
+      <c r="G94" t="n">
+        <v>43.31300152442923</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2620,6 +3188,12 @@
           <t>SE SIENRA</t>
         </is>
       </c>
+      <c r="F95" t="n">
+        <v>-6.541087896123271</v>
+      </c>
+      <c r="G95" t="n">
+        <v>43.16516363580312</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2643,6 +3217,12 @@
           <t>SE SAN ESTEBAN</t>
         </is>
       </c>
+      <c r="F96" t="n">
+        <v>-5.829568086654855</v>
+      </c>
+      <c r="G96" t="n">
+        <v>43.34468808918069</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2666,6 +3246,12 @@
           <t>SE SALAS</t>
         </is>
       </c>
+      <c r="F97" t="n">
+        <v>-6.300200711303158</v>
+      </c>
+      <c r="G97" t="n">
+        <v>43.36653058765098</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2689,6 +3275,12 @@
           <t>SE SAGUNTO</t>
         </is>
       </c>
+      <c r="F98" t="n">
+        <v>-0.2682287395933881</v>
+      </c>
+      <c r="G98" t="n">
+        <v>39.67320669999805</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2712,6 +3304,12 @@
           <t>SE ROMIO</t>
         </is>
       </c>
+      <c r="F99" t="n">
+        <v>-6.002437769756098</v>
+      </c>
+      <c r="G99" t="n">
+        <v>43.48162029707475</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2735,6 +3333,12 @@
           <t>SE ROJALES</t>
         </is>
       </c>
+      <c r="F100" t="n">
+        <v>-0.7375155058982014</v>
+      </c>
+      <c r="G100" t="n">
+        <v>38.05543816954679</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2758,6 +3362,12 @@
           <t>SE RIBADESELLA</t>
         </is>
       </c>
+      <c r="F101" t="n">
+        <v>-5.079581584449081</v>
+      </c>
+      <c r="G101" t="n">
+        <v>43.45512531820759</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2781,6 +3391,12 @@
           <t>SE QUINTANA</t>
         </is>
       </c>
+      <c r="F102" t="n">
+        <v>-5.530277616528415</v>
+      </c>
+      <c r="G102" t="n">
+        <v>43.37179028650448</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2804,6 +3420,12 @@
           <t>SE QUART DEL POBLET</t>
         </is>
       </c>
+      <c r="F103" t="n">
+        <v>-0.5265454494263143</v>
+      </c>
+      <c r="G103" t="n">
+        <v>39.48075603016901</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2827,6 +3449,12 @@
           <t>SE PUMARIN</t>
         </is>
       </c>
+      <c r="F104" t="n">
+        <v>-5.687732229329174</v>
+      </c>
+      <c r="G104" t="n">
+        <v>43.51821069781276</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2850,6 +3478,12 @@
           <t>SE PUERTO DE GIJON</t>
         </is>
       </c>
+      <c r="F105" t="n">
+        <v>-5.69882728587994</v>
+      </c>
+      <c r="G105" t="n">
+        <v>43.56954087205954</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2873,6 +3507,12 @@
           <t>SE PUERTO</t>
         </is>
       </c>
+      <c r="F106" t="n">
+        <v>-5.930297624341967</v>
+      </c>
+      <c r="G106" t="n">
+        <v>43.32390714990341</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2896,6 +3536,12 @@
           <t>SE PUEBLA DE RODA</t>
         </is>
       </c>
+      <c r="F107" t="n">
+        <v>0.5405912150936508</v>
+      </c>
+      <c r="G107" t="n">
+        <v>42.30262638554914</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2919,6 +3565,12 @@
           <t>SE PROAZA CENTRAL</t>
         </is>
       </c>
+      <c r="F108" t="n">
+        <v>-6.017603394774929</v>
+      </c>
+      <c r="G108" t="n">
+        <v>43.24901189186276</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2942,6 +3594,12 @@
           <t>SE PRIAÑES</t>
         </is>
       </c>
+      <c r="F109" t="n">
+        <v>-5.976625064709956</v>
+      </c>
+      <c r="G109" t="n">
+        <v>43.38312916439408</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2965,6 +3623,12 @@
           <t>SE PRAVIA</t>
         </is>
       </c>
+      <c r="F110" t="n">
+        <v>-6.16820268173752</v>
+      </c>
+      <c r="G110" t="n">
+        <v>43.46861056836972</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2988,6 +3652,12 @@
           <t>SE PINTO AYUDEN</t>
         </is>
       </c>
+      <c r="F111" t="n">
+        <v>-3.723059621297923</v>
+      </c>
+      <c r="G111" t="n">
+        <v>40.26357894047216</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3011,6 +3681,12 @@
           <t>SE PANES</t>
         </is>
       </c>
+      <c r="F112" t="n">
+        <v>-4.582727387822273</v>
+      </c>
+      <c r="G112" t="n">
+        <v>43.32384219215471</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3034,6 +3710,12 @@
           <t>SE MIRANDA</t>
         </is>
       </c>
+      <c r="F113" t="n">
+        <v>-6.203925966887598</v>
+      </c>
+      <c r="G113" t="n">
+        <v>43.33158684833028</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3057,6 +3739,12 @@
           <t>SE MERES</t>
         </is>
       </c>
+      <c r="F114" t="n">
+        <v>-5.756185813212351</v>
+      </c>
+      <c r="G114" t="n">
+        <v>43.37928984817002</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3080,6 +3768,12 @@
           <t>SE MARUCA</t>
         </is>
       </c>
+      <c r="F115" t="n">
+        <v>-5.925722077204804</v>
+      </c>
+      <c r="G115" t="n">
+        <v>43.57337751148633</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3103,6 +3797,12 @@
           <t>SE LOS VIENTOS</t>
         </is>
       </c>
+      <c r="F116" t="n">
+        <v>-1.139597056808286</v>
+      </c>
+      <c r="G116" t="n">
+        <v>41.49438893902957</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3126,6 +3826,12 @@
           <t>SE LLOREDA</t>
         </is>
       </c>
+      <c r="F117" t="n">
+        <v>-5.701921125667845</v>
+      </c>
+      <c r="G117" t="n">
+        <v>43.52356739032355</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3149,6 +3855,12 @@
           <t>SE LLANES</t>
         </is>
       </c>
+      <c r="F118" t="n">
+        <v>-4.768188621274161</v>
+      </c>
+      <c r="G118" t="n">
+        <v>43.40157121717201</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3172,6 +3884,12 @@
           <t>SE LANGREO</t>
         </is>
       </c>
+      <c r="F119" t="n">
+        <v>-5.693323928846504</v>
+      </c>
+      <c r="G119" t="n">
+        <v>43.31824682458355</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3195,6 +3913,12 @@
           <t>SE LA RIERA</t>
         </is>
       </c>
+      <c r="F120" t="n">
+        <v>-6.260167997263993</v>
+      </c>
+      <c r="G120" t="n">
+        <v>43.15326033055474</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3218,6 +3942,12 @@
           <t>SE LA MALVA</t>
         </is>
       </c>
+      <c r="F121" t="n">
+        <v>-6.252497735187372</v>
+      </c>
+      <c r="G121" t="n">
+        <v>43.1162545045186</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3241,6 +3971,12 @@
           <t>SE LA FLORIDA</t>
         </is>
       </c>
+      <c r="F122" t="n">
+        <v>-6.414261051908827</v>
+      </c>
+      <c r="G122" t="n">
+        <v>43.28847967706643</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3264,6 +4000,12 @@
           <t>SE LA BARCA</t>
         </is>
       </c>
+      <c r="F123" t="n">
+        <v>-6.303989798800601</v>
+      </c>
+      <c r="G123" t="n">
+        <v>43.32104673064823</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3287,6 +4029,12 @@
           <t>SE ISABENA</t>
         </is>
       </c>
+      <c r="F124" t="n">
+        <v>0.5388376412120065</v>
+      </c>
+      <c r="G124" t="n">
+        <v>42.30367063239313</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3310,6 +4058,12 @@
           <t>SE GRADO</t>
         </is>
       </c>
+      <c r="F125" t="n">
+        <v>-5.99443065689294</v>
+      </c>
+      <c r="G125" t="n">
+        <v>43.38932519204795</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3333,6 +4087,12 @@
           <t>SE GIJON NORTE</t>
         </is>
       </c>
+      <c r="F126" t="n">
+        <v>-5.684376343645138</v>
+      </c>
+      <c r="G126" t="n">
+        <v>43.53322139174804</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3356,6 +4116,12 @@
           <t>SE ELCHE</t>
         </is>
       </c>
+      <c r="F127" t="n">
+        <v>-0.6360089217040161</v>
+      </c>
+      <c r="G127" t="n">
+        <v>38.26417854050175</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3379,6 +4145,12 @@
           <t>SE EL VASCO</t>
         </is>
       </c>
+      <c r="F128" t="n">
+        <v>-5.841934375811386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>43.36523098033493</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3402,6 +4174,12 @@
           <t>SE EL SABINAR</t>
         </is>
       </c>
+      <c r="F129" t="n">
+        <v>-1.20493089129256</v>
+      </c>
+      <c r="G129" t="n">
+        <v>41.55528031021836</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3425,6 +4203,12 @@
           <t>SE CUDILLERO</t>
         </is>
       </c>
+      <c r="F130" t="n">
+        <v>-6.158409167885106</v>
+      </c>
+      <c r="G130" t="n">
+        <v>43.55359749499419</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3448,6 +4232,12 @@
           <t>SE CORREDORIA</t>
         </is>
       </c>
+      <c r="F131" t="n">
+        <v>-5.828556981222503</v>
+      </c>
+      <c r="G131" t="n">
+        <v>43.3823633656427</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3471,6 +4261,12 @@
           <t>SE COLUNGA</t>
         </is>
       </c>
+      <c r="F132" t="n">
+        <v>-5.255593684347911</v>
+      </c>
+      <c r="G132" t="n">
+        <v>43.48215296835979</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3494,6 +4290,12 @@
           <t>SE CASTRO</t>
         </is>
       </c>
+      <c r="F133" t="n">
+        <v>-5.806150883080035</v>
+      </c>
+      <c r="G133" t="n">
+        <v>43.40724641880979</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3517,6 +4319,12 @@
           <t>SE CASTIELLO</t>
         </is>
       </c>
+      <c r="F134" t="n">
+        <v>-5.643633405383263</v>
+      </c>
+      <c r="G134" t="n">
+        <v>43.51886976720146</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3540,6 +4348,12 @@
           <t>SE CARROCERA II</t>
         </is>
       </c>
+      <c r="F135" t="n">
+        <v>-5.623498073382827</v>
+      </c>
+      <c r="G135" t="n">
+        <v>43.28817341080597</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3563,6 +4377,12 @@
           <t>SE CARRIO</t>
         </is>
       </c>
+      <c r="F136" t="n">
+        <v>-5.728512926116953</v>
+      </c>
+      <c r="G136" t="n">
+        <v>43.55595643253569</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3586,6 +4406,12 @@
           <t>SE CARREÑA</t>
         </is>
       </c>
+      <c r="F137" t="n">
+        <v>-4.851275103049105</v>
+      </c>
+      <c r="G137" t="n">
+        <v>43.31568655448488</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3609,6 +4435,12 @@
           <t>SE CAMPORRIONDI 1</t>
         </is>
       </c>
+      <c r="F138" t="n">
+        <v>-5.107565124951138</v>
+      </c>
+      <c r="G138" t="n">
+        <v>43.25103605021433</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3632,6 +4464,12 @@
           <t>SE CAMARMEÑA</t>
         </is>
       </c>
+      <c r="F139" t="n">
+        <v>-4.83100555119789</v>
+      </c>
+      <c r="G139" t="n">
+        <v>43.25918708708115</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3655,6 +4493,12 @@
           <t>SE C.T. NARCEA</t>
         </is>
       </c>
+      <c r="F140" t="n">
+        <v>-5.541019638328521</v>
+      </c>
+      <c r="G140" t="n">
+        <v>43.32087761628595</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3678,6 +4522,12 @@
           <t>SE ARRIONDAS</t>
         </is>
       </c>
+      <c r="F141" t="n">
+        <v>-5.192120917302637</v>
+      </c>
+      <c r="G141" t="n">
+        <v>43.40182986169689</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3701,6 +4551,12 @@
           <t>SE AMBULATORIO</t>
         </is>
       </c>
+      <c r="F142" t="n">
+        <v>-5.917709462114769</v>
+      </c>
+      <c r="G142" t="n">
+        <v>43.55336000713393</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3724,6 +4580,12 @@
           <t>SE ALIMERKA</t>
         </is>
       </c>
+      <c r="F143" t="n">
+        <v>-5.798755484460995</v>
+      </c>
+      <c r="G143" t="n">
+        <v>43.4448576326113</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3747,6 +4609,12 @@
           <t>SE ALDAIA</t>
         </is>
       </c>
+      <c r="F144" t="n">
+        <v>-0.5004668866569091</v>
+      </c>
+      <c r="G144" t="n">
+        <v>39.45221510035838</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3769,6 +4637,12 @@
         <is>
           <t>SE PLANS DE LA SALA</t>
         </is>
+      </c>
+      <c r="F145" t="n">
+        <v>1.900464533802391</v>
+      </c>
+      <c r="G145" t="n">
+        <v>41.78263772933386</v>
       </c>
     </row>
   </sheetData>

--- a/Distribucion/Excels/EREDES.xlsx
+++ b/Distribucion/Excels/EREDES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>Latitud</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>43.40423007016015</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>43.36166549797462</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>43.51382652357489</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>43.32965206422116</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>43.61139725656262</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>43.22241801284392</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>40.25074248606446</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>39.47656310040726</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>43.28389619268847</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>43.31515269439987</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>43.33664010341921</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>43.38749649272513</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -842,6 +907,11 @@
       <c r="G14" t="n">
         <v>43.55154199568497</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -871,6 +941,11 @@
       <c r="G15" t="n">
         <v>43.29292772470937</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -901,6 +976,11 @@
       <c r="G16" t="n">
         <v>43.51335593219567</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -930,6 +1010,11 @@
       <c r="G17" t="n">
         <v>43.221842778572</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -959,6 +1044,11 @@
       <c r="G18" t="n">
         <v>43.32329127758536</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -988,6 +1078,11 @@
       <c r="G19" t="n">
         <v>43.52569826350171</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1017,6 +1112,11 @@
       <c r="G20" t="n">
         <v>43.24923204463798</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1046,6 +1146,11 @@
       <c r="G21" t="n">
         <v>43.36199230624374</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1075,6 +1180,11 @@
       <c r="G22" t="n">
         <v>43.5714077688927</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1104,6 +1214,11 @@
       <c r="G23" t="n">
         <v>38.14265999935877</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1133,6 +1248,11 @@
       <c r="G24" t="n">
         <v>43.48795432270181</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1163,6 +1283,11 @@
       <c r="G25" t="n">
         <v>43.35910332658035</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1192,6 +1317,11 @@
       <c r="G26" t="n">
         <v>43.54123537069653</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1221,6 +1351,11 @@
       <c r="G27" t="n">
         <v>43.43290995128635</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1250,6 +1385,11 @@
       <c r="G28" t="n">
         <v>43.3920805403917</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1279,6 +1419,11 @@
       <c r="G29" t="n">
         <v>43.34917008708607</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1308,6 +1453,11 @@
       <c r="G30" t="n">
         <v>43.36988666312457</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1337,6 +1487,11 @@
       <c r="G31" t="n">
         <v>43.5402103326235</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1366,6 +1521,11 @@
       <c r="G32" t="n">
         <v>39.48060150903018</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1395,6 +1555,11 @@
       <c r="G33" t="n">
         <v>43.3885883037095</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1424,6 +1589,11 @@
       <c r="G34" t="n">
         <v>42.922850630306</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1454,6 +1624,11 @@
       <c r="G35" t="n">
         <v>43.35134996388585</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1483,6 +1658,11 @@
       <c r="G36" t="n">
         <v>43.41491873745129</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1512,6 +1692,11 @@
       <c r="G37" t="n">
         <v>43.38170404107714</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1541,6 +1726,11 @@
       <c r="G38" t="n">
         <v>43.24250836440902</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1570,6 +1760,11 @@
       <c r="G39" t="n">
         <v>42.20442107182719</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1599,6 +1794,11 @@
       <c r="G40" t="n">
         <v>43.29924964357859</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1628,6 +1828,11 @@
       <c r="G41" t="n">
         <v>39.67165958209399</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1657,6 +1862,11 @@
       <c r="G42" t="n">
         <v>43.34400148565084</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1686,6 +1896,11 @@
       <c r="G43" t="n">
         <v>43.49061795940048</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1715,6 +1930,11 @@
       <c r="G44" t="n">
         <v>43.40266501734791</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1744,6 +1964,11 @@
       <c r="G45" t="n">
         <v>43.50306336406747</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1773,6 +1998,11 @@
       <c r="G46" t="n">
         <v>43.55721738456101</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1802,6 +2032,11 @@
       <c r="G47" t="n">
         <v>43.17857177824941</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1831,6 +2066,11 @@
       <c r="G48" t="n">
         <v>43.03173536874539</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1860,6 +2100,11 @@
       <c r="G49" t="n">
         <v>43.44253213868278</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1889,6 +2134,11 @@
       <c r="G50" t="n">
         <v>40.27402816098827</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1918,6 +2168,11 @@
       <c r="G51" t="n">
         <v>43.34456438526159</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1947,6 +2202,11 @@
       <c r="G52" t="n">
         <v>43.53930645642332</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1976,6 +2236,11 @@
       <c r="G53" t="n">
         <v>43.17168445197187</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2005,6 +2270,11 @@
       <c r="G54" t="n">
         <v>38.05340377483826</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2034,6 +2304,11 @@
       <c r="G55" t="n">
         <v>43.22724877127121</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2063,6 +2338,11 @@
       <c r="G56" t="n">
         <v>43.53328253553471</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2092,6 +2372,11 @@
       <c r="G57" t="n">
         <v>43.35656957720781</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2121,6 +2406,11 @@
       <c r="G58" t="n">
         <v>43.35385355909192</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2150,6 +2440,11 @@
       <c r="G59" t="n">
         <v>43.45635731330629</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2179,6 +2474,11 @@
       <c r="G60" t="n">
         <v>43.38644432631414</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2208,6 +2508,11 @@
       <c r="G61" t="n">
         <v>43.35780813251858</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2237,6 +2542,11 @@
       <c r="G62" t="n">
         <v>39.44724442938274</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2266,6 +2576,11 @@
       <c r="G63" t="n">
         <v>41.64228551689076</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2295,6 +2610,11 @@
       <c r="G64" t="n">
         <v>43.54031903261445</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2324,6 +2644,11 @@
       <c r="G65" t="n">
         <v>43.41142164123818</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2353,6 +2678,11 @@
       <c r="G66" t="n">
         <v>43.52550235091994</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2382,6 +2712,11 @@
       <c r="G67" t="n">
         <v>43.38704217495874</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2411,6 +2746,11 @@
       <c r="G68" t="n">
         <v>43.28628333345606</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2440,6 +2780,11 @@
       <c r="G69" t="n">
         <v>43.28756734665058</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2469,6 +2814,11 @@
       <c r="G70" t="n">
         <v>43.32369818153472</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2498,6 +2848,11 @@
       <c r="G71" t="n">
         <v>39.68134071396904</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2527,6 +2882,11 @@
       <c r="G72" t="n">
         <v>39.47051918336894</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2556,6 +2916,11 @@
       <c r="G73" t="n">
         <v>39.47240528459459</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2585,6 +2950,11 @@
       <c r="G74" t="n">
         <v>39.47240426706473</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2614,6 +2984,11 @@
       <c r="G75" t="n">
         <v>43.60872826659367</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2643,6 +3018,11 @@
       <c r="G76" t="n">
         <v>43.27007106759447</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2672,6 +3052,11 @@
       <c r="G77" t="n">
         <v>43.4273505112372</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2701,6 +3086,11 @@
       <c r="G78" t="n">
         <v>41.63369428097609</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2730,6 +3120,11 @@
       <c r="G79" t="n">
         <v>43.49175589799071</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2759,6 +3154,11 @@
       <c r="G80" t="n">
         <v>43.2903108329393</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2788,6 +3188,11 @@
       <c r="G81" t="n">
         <v>42.41897114122447</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2817,6 +3222,11 @@
       <c r="G82" t="n">
         <v>43.36768325268325</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2846,6 +3256,11 @@
       <c r="G83" t="n">
         <v>39.53191787891437</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2875,6 +3290,11 @@
       <c r="G84" t="n">
         <v>43.44755057328947</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2904,6 +3324,11 @@
       <c r="G85" t="n">
         <v>43.55833761510075</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2933,6 +3358,11 @@
       <c r="G86" t="n">
         <v>43.20278998614728</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2962,6 +3392,11 @@
       <c r="G87" t="n">
         <v>43.47428259734419</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2991,6 +3426,11 @@
       <c r="G88" t="n">
         <v>43.54634210382199</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3020,6 +3460,11 @@
       <c r="G89" t="n">
         <v>39.67404886438688</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3049,6 +3494,11 @@
       <c r="G90" t="n">
         <v>43.33003659789201</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3078,6 +3528,11 @@
       <c r="G91" t="n">
         <v>43.04980597251483</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3107,6 +3562,11 @@
       <c r="G92" t="n">
         <v>43.55182645805944</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3136,6 +3596,11 @@
       <c r="G93" t="n">
         <v>43.57446717789744</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3165,6 +3630,11 @@
       <c r="G94" t="n">
         <v>43.31300152442923</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3194,6 +3664,11 @@
       <c r="G95" t="n">
         <v>43.16516363580312</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3223,6 +3698,11 @@
       <c r="G96" t="n">
         <v>43.34468808918069</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3252,6 +3732,11 @@
       <c r="G97" t="n">
         <v>43.36653058765098</v>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3281,6 +3766,11 @@
       <c r="G98" t="n">
         <v>39.67320669999805</v>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3310,6 +3800,11 @@
       <c r="G99" t="n">
         <v>43.48162029707475</v>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3339,6 +3834,11 @@
       <c r="G100" t="n">
         <v>38.05543816954679</v>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3368,6 +3868,11 @@
       <c r="G101" t="n">
         <v>43.45512531820759</v>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3397,6 +3902,11 @@
       <c r="G102" t="n">
         <v>43.37179028650448</v>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3426,6 +3936,11 @@
       <c r="G103" t="n">
         <v>39.48075603016901</v>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3455,6 +3970,11 @@
       <c r="G104" t="n">
         <v>43.51821069781276</v>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3484,6 +4004,11 @@
       <c r="G105" t="n">
         <v>43.56954087205954</v>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3513,6 +4038,11 @@
       <c r="G106" t="n">
         <v>43.32390714990341</v>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3542,6 +4072,11 @@
       <c r="G107" t="n">
         <v>42.30262638554914</v>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3571,6 +4106,11 @@
       <c r="G108" t="n">
         <v>43.24901189186276</v>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3600,6 +4140,11 @@
       <c r="G109" t="n">
         <v>43.38312916439408</v>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3629,6 +4174,11 @@
       <c r="G110" t="n">
         <v>43.46861056836972</v>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3658,6 +4208,11 @@
       <c r="G111" t="n">
         <v>40.26357894047216</v>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Comunidad de Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3687,6 +4242,11 @@
       <c r="G112" t="n">
         <v>43.32384219215471</v>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3716,6 +4276,11 @@
       <c r="G113" t="n">
         <v>43.33158684833028</v>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3745,6 +4310,11 @@
       <c r="G114" t="n">
         <v>43.37928984817002</v>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3774,6 +4344,11 @@
       <c r="G115" t="n">
         <v>43.57337751148633</v>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3803,6 +4378,11 @@
       <c r="G116" t="n">
         <v>41.49438893902957</v>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3832,6 +4412,11 @@
       <c r="G117" t="n">
         <v>43.52356739032355</v>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3861,6 +4446,11 @@
       <c r="G118" t="n">
         <v>43.40157121717201</v>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3890,6 +4480,11 @@
       <c r="G119" t="n">
         <v>43.31824682458355</v>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3919,6 +4514,11 @@
       <c r="G120" t="n">
         <v>43.15326033055474</v>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3948,6 +4548,11 @@
       <c r="G121" t="n">
         <v>43.1162545045186</v>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3977,6 +4582,11 @@
       <c r="G122" t="n">
         <v>43.28847967706643</v>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4006,6 +4616,11 @@
       <c r="G123" t="n">
         <v>43.32104673064823</v>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4035,6 +4650,11 @@
       <c r="G124" t="n">
         <v>42.30367063239313</v>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4064,6 +4684,11 @@
       <c r="G125" t="n">
         <v>43.38932519204795</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4093,6 +4718,11 @@
       <c r="G126" t="n">
         <v>43.53322139174804</v>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4122,6 +4752,11 @@
       <c r="G127" t="n">
         <v>38.26417854050175</v>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4151,6 +4786,11 @@
       <c r="G128" t="n">
         <v>43.36523098033493</v>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4180,6 +4820,11 @@
       <c r="G129" t="n">
         <v>41.55528031021836</v>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Aragón</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4209,6 +4854,11 @@
       <c r="G130" t="n">
         <v>43.55359749499419</v>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4238,6 +4888,11 @@
       <c r="G131" t="n">
         <v>43.3823633656427</v>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4267,6 +4922,11 @@
       <c r="G132" t="n">
         <v>43.48215296835979</v>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4296,6 +4956,11 @@
       <c r="G133" t="n">
         <v>43.40724641880979</v>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4325,6 +4990,11 @@
       <c r="G134" t="n">
         <v>43.51886976720146</v>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4354,6 +5024,11 @@
       <c r="G135" t="n">
         <v>43.28817341080597</v>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4383,6 +5058,11 @@
       <c r="G136" t="n">
         <v>43.55595643253569</v>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4412,6 +5092,11 @@
       <c r="G137" t="n">
         <v>43.31568655448488</v>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4441,6 +5126,11 @@
       <c r="G138" t="n">
         <v>43.25103605021433</v>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4470,6 +5160,11 @@
       <c r="G139" t="n">
         <v>43.25918708708115</v>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4499,6 +5194,11 @@
       <c r="G140" t="n">
         <v>43.32087761628595</v>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4528,6 +5228,11 @@
       <c r="G141" t="n">
         <v>43.40182986169689</v>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4557,6 +5262,11 @@
       <c r="G142" t="n">
         <v>43.55336000713393</v>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4586,6 +5296,11 @@
       <c r="G143" t="n">
         <v>43.4448576326113</v>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4615,6 +5330,11 @@
       <c r="G144" t="n">
         <v>39.45221510035838</v>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Comunidad Valenciana</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4643,6 +5363,11 @@
       </c>
       <c r="G145" t="n">
         <v>41.78263772933386</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Cataluña</t>
+        </is>
       </c>
     </row>
   </sheetData>
